--- a/docs/migration/SISKOP-Template-Migrasi-Laporan.xlsx
+++ b/docs/migration/SISKOP-Template-Migrasi-Laporan.xlsx
@@ -201,7 +201,7 @@
     <t>7_Pinjaman</t>
   </si>
   <si>
-    <t>WAJIB. Sisa pembiayaan per anggota dari lampiran RAT. Laporan tidak memuat plafon, tenor, atau tanggal cair, jadi sistem membuat nilai pengganti dan menandainya di Catatan. KOL dan jatuh tempo TIDAK akurat sampai kontrak asli dimasukkan.</t>
+    <t>opsional. Sisa pembiayaan per anggota dari lampiran RAT. Laporan tidak memuat plafon, tenor, atau tanggal cair, jadi sistem membuat nilai pengganti dan menandainya di Catatan. KOL dan jatuh tempo TIDAK akurat sampai kontrak asli dimasukkan. Kosongkan sheet ini bila koperasi belum punya pinjaman.</t>
   </si>
   <si>
     <t>9_Neraca</t>
@@ -45749,7 +45749,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF1F3A5F"/>
+    <tabColor rgb="FF6B7280"/>
   </sheetPr>
   <dimension ref="A1:J1003"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
